--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T10:38:49+00:00</t>
+    <t>2025-02-11T11:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-head-circum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
